--- a/news_daily/2026-08-18.xlsx
+++ b/news_daily/2026-08-18.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BH$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BH$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BH$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BH$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -43,7 +43,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -58,11 +58,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFE0B2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFCDD2"/>
       </patternFill>
     </fill>
   </fills>
@@ -84,15 +79,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -463,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH10"/>
+  <dimension ref="A1:BL10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -526,6 +518,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -829,6 +825,26 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -841,7 +857,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr"/>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Walt Disney Company (The)</t>
@@ -875,17 +895,17 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -934,7 +954,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>32beac2ca3c64d5cab7fe72d730bb172</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>e394e6a4e994de361a644b0f</t>
@@ -957,7 +981,7 @@
       <c r="AN2" s="2" t="inlineStr"/>
       <c r="AO2" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP2" s="2" t="inlineStr"/>
@@ -999,6 +1023,22 @@
       </c>
       <c r="BG2" s="2" t="inlineStr"/>
       <c r="BH2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="BJ2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -1034,28 +1074,32 @@
       <c r="G3" s="3" t="inlineStr"/>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>破產</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -1095,7 +1139,7 @@
       </c>
       <c r="Y3" s="3" t="inlineStr">
         <is>
-          <t>BANKRUPTCY</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z3" s="3" t="inlineStr">
@@ -1108,7 +1152,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB3" s="3" t="inlineStr"/>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>79e31a1c015247efb28b3368d5551d2b</t>
+        </is>
+      </c>
       <c r="AC3" s="3" t="inlineStr">
         <is>
           <t>5f384da3250c133e5ee2f6b0</t>
@@ -1129,7 +1177,11 @@
       <c r="AL3" s="3" t="inlineStr"/>
       <c r="AM3" s="3" t="inlineStr"/>
       <c r="AN3" s="3" t="inlineStr"/>
-      <c r="AO3" s="3" t="inlineStr"/>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP3" s="3" t="inlineStr"/>
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr"/>
@@ -1165,702 +1217,734 @@
         </is>
       </c>
       <c r="BH3" s="3" t="inlineStr"/>
+      <c r="BI3" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ3" s="3" t="inlineStr"/>
+      <c r="BK3" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>EIX</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Edison International Common Stock</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>2026-08-18T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Edison International Gains as Investors Weigh Reaffirmed Outlook and Wildfire Liability Developments</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>天災</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L4" s="4" t="inlineStr"/>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr"/>
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O4" s="4" t="inlineStr">
+      <c r="O4" s="3" t="inlineStr">
         <is>
           <t>0.726</t>
         </is>
       </c>
-      <c r="P4" s="4" t="inlineStr"/>
-      <c r="Q4" s="4" t="inlineStr"/>
-      <c r="R4" s="4" t="inlineStr"/>
-      <c r="S4" s="4" t="inlineStr"/>
-      <c r="T4" s="4" t="inlineStr">
+      <c r="P4" s="3" t="inlineStr"/>
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr"/>
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U4" s="4" t="inlineStr">
+      <c r="U4" s="3" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxOcnJLelFtVGpjdlZ0WkxidFlJMUcyQmF0NWR2QUEyQUF3eGNQNDZ5bVlaNThUMmRtVUNVOWJ0V0t2NW9oS2ctZGJEWHNZaHlGRFdldXJTQ2hDLVdHTDBfeTlacXRxaWhtNVo1Q0JCcDFja2RGTUVwN0ctTFZMOTEwOExpQU9nU0ZlRk84MF9SdFlDUXM3bjhIQnlybVdRckF0OHFnOS1qNnVCTUF0T1llSUlmaWZmLW5pMkIxQjVsaXdfeDZoYXA0TkZGMDJJUQ?oc=5</t>
         </is>
       </c>
-      <c r="V4" s="4" t="inlineStr">
+      <c r="V4" s="3" t="inlineStr">
         <is>
           <t>Quiver Quantitative</t>
         </is>
       </c>
-      <c r="W4" s="4" t="inlineStr"/>
-      <c r="X4" s="4" t="inlineStr">
+      <c r="W4" s="3" t="inlineStr"/>
+      <c r="X4" s="3" t="inlineStr">
         <is>
           <t>OPERATIONS</t>
         </is>
       </c>
-      <c r="Y4" s="4" t="inlineStr">
+      <c r="Y4" s="3" t="inlineStr">
         <is>
           <t>NATURAL_DISASTER</t>
         </is>
       </c>
-      <c r="Z4" s="4" t="inlineStr">
+      <c r="Z4" s="3" t="inlineStr">
         <is>
           <t>wildfire</t>
         </is>
       </c>
-      <c r="AA4" s="4" t="inlineStr">
+      <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB4" s="4" t="inlineStr"/>
-      <c r="AC4" s="4" t="inlineStr">
+      <c r="AB4" s="3" t="inlineStr"/>
+      <c r="AC4" s="3" t="inlineStr">
         <is>
           <t>cdaff806a3e2c472542a3b8e</t>
         </is>
       </c>
-      <c r="AD4" s="4" t="inlineStr">
+      <c r="AD4" s="3" t="inlineStr">
         <is>
           <t>7872ffad519f37fd7e26250b</t>
         </is>
       </c>
-      <c r="AE4" s="4" t="inlineStr"/>
-      <c r="AF4" s="4" t="inlineStr"/>
-      <c r="AG4" s="4" t="inlineStr"/>
-      <c r="AH4" s="4" t="inlineStr"/>
-      <c r="AI4" s="4" t="inlineStr"/>
-      <c r="AJ4" s="4" t="inlineStr"/>
-      <c r="AK4" s="4" t="inlineStr"/>
-      <c r="AL4" s="4" t="inlineStr"/>
-      <c r="AM4" s="4" t="inlineStr"/>
-      <c r="AN4" s="4" t="inlineStr"/>
-      <c r="AO4" s="4" t="inlineStr"/>
-      <c r="AP4" s="4" t="inlineStr"/>
-      <c r="AQ4" s="4" t="inlineStr"/>
-      <c r="AR4" s="4" t="inlineStr"/>
-      <c r="AS4" s="4" t="inlineStr"/>
-      <c r="AT4" s="4" t="inlineStr"/>
-      <c r="AU4" s="4" t="inlineStr"/>
-      <c r="AV4" s="4" t="inlineStr"/>
-      <c r="AW4" s="4" t="inlineStr">
+      <c r="AE4" s="3" t="inlineStr"/>
+      <c r="AF4" s="3" t="inlineStr"/>
+      <c r="AG4" s="3" t="inlineStr"/>
+      <c r="AH4" s="3" t="inlineStr"/>
+      <c r="AI4" s="3" t="inlineStr"/>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" s="3" t="inlineStr"/>
+      <c r="AM4" s="3" t="inlineStr"/>
+      <c r="AN4" s="3" t="inlineStr"/>
+      <c r="AO4" s="3" t="inlineStr"/>
+      <c r="AP4" s="3" t="inlineStr"/>
+      <c r="AQ4" s="3" t="inlineStr"/>
+      <c r="AR4" s="3" t="inlineStr"/>
+      <c r="AS4" s="3" t="inlineStr"/>
+      <c r="AT4" s="3" t="inlineStr"/>
+      <c r="AU4" s="3" t="inlineStr"/>
+      <c r="AV4" s="3" t="inlineStr"/>
+      <c r="AW4" s="3" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX4" s="4" t="inlineStr"/>
-      <c r="AY4" s="4" t="inlineStr"/>
-      <c r="AZ4" s="4" t="inlineStr"/>
-      <c r="BA4" s="4" t="inlineStr"/>
-      <c r="BB4" s="4" t="inlineStr">
+      <c r="AX4" s="3" t="inlineStr"/>
+      <c r="AY4" s="3" t="inlineStr"/>
+      <c r="AZ4" s="3" t="inlineStr"/>
+      <c r="BA4" s="3" t="inlineStr"/>
+      <c r="BB4" s="3" t="inlineStr">
         <is>
           <t>EIX</t>
         </is>
       </c>
-      <c r="BC4" s="4" t="inlineStr">
+      <c r="BC4" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD4" s="4" t="inlineStr"/>
-      <c r="BE4" s="4" t="inlineStr">
+      <c r="BD4" s="3" t="inlineStr"/>
+      <c r="BE4" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF4" s="4" t="inlineStr">
+      <c r="BF4" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG4" s="4" t="inlineStr">
+      <c r="BG4" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH4" s="4" t="inlineStr"/>
+      <c r="BH4" s="3" t="inlineStr"/>
+      <c r="BI4" s="3" t="inlineStr"/>
+      <c r="BJ4" s="3" t="inlineStr"/>
+      <c r="BK4" s="3" t="inlineStr"/>
+      <c r="BL4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr"/>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr"/>
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Cencora</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>2026-08-18T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>What: Public Safety Patrol When: August 19, 2026 1003H Where: Bluementritt cor. España Blvd. Status: Negative for flooded area as of 1003H Unit: DMAX3 T.O: B. Mendoza Crew: B. Santos (Source: Manila City DRRM Department) #ManilaPIO #AlertoManile</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr"/>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>天災</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L5" s="4" t="inlineStr">
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>待人工覆核</t>
         </is>
       </c>
-      <c r="M5" s="4" t="inlineStr">
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N5" s="4" t="inlineStr">
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O5" s="4" t="inlineStr">
+      <c r="O5" s="3" t="inlineStr">
         <is>
           <t>'-0.108</t>
         </is>
       </c>
-      <c r="P5" s="4" t="inlineStr"/>
-      <c r="Q5" s="4" t="inlineStr"/>
-      <c r="R5" s="4" t="inlineStr"/>
-      <c r="S5" s="4" t="inlineStr"/>
-      <c r="T5" s="4" t="inlineStr">
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr"/>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr">
         <is>
           <t>主體證據不足</t>
         </is>
       </c>
-      <c r="U5" s="4" t="inlineStr">
+      <c r="U5" s="3" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxNTXNvREY3UzJxS0ZXNnRQUy1XUGVneThKNTFMc2N6OXV4RGZRcEE3UXJjNzBHU3h1a1NqQnVMMTlRcEFDY3I3eFk3ZUlnVWJURGJUeFNoTjdGTEZ0QmItVlhENVpJMEs0Ymp0Sk5lUlNLNUc1SlNlNW0ybC1jZjR6Z0tiakJFYmMyNGVCenNGTW8tOFVrdGFVOG15NlhURTRNeTktaFM1TVNLWEtIdFVMZDY4UXJtR3p2S0ExZllRbVNTYkQ1djhrX0JpVUJMT1JINmxKUU00R3NCa2E5?oc=5</t>
         </is>
       </c>
-      <c r="V5" s="4" t="inlineStr">
+      <c r="V5" s="3" t="inlineStr">
         <is>
           <t>facebook.com</t>
         </is>
       </c>
-      <c r="W5" s="4" t="inlineStr"/>
-      <c r="X5" s="4" t="inlineStr">
+      <c r="W5" s="3" t="inlineStr"/>
+      <c r="X5" s="3" t="inlineStr">
         <is>
           <t>OPERATIONS</t>
         </is>
       </c>
-      <c r="Y5" s="4" t="inlineStr">
+      <c r="Y5" s="3" t="inlineStr">
         <is>
           <t>NATURAL_DISASTER</t>
         </is>
       </c>
-      <c r="Z5" s="4" t="inlineStr">
+      <c r="Z5" s="3" t="inlineStr">
         <is>
           <t>flood</t>
         </is>
       </c>
-      <c r="AA5" s="4" t="inlineStr">
+      <c r="AA5" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB5" s="4" t="inlineStr"/>
-      <c r="AC5" s="4" t="inlineStr">
+      <c r="AB5" s="3" t="inlineStr"/>
+      <c r="AC5" s="3" t="inlineStr">
         <is>
           <t>304cbada68fbab61665c24fd</t>
         </is>
       </c>
-      <c r="AD5" s="4" t="inlineStr">
+      <c r="AD5" s="3" t="inlineStr">
         <is>
           <t>cef13a3c747e25f7c286fb7c</t>
         </is>
       </c>
-      <c r="AE5" s="4" t="inlineStr"/>
-      <c r="AF5" s="4" t="inlineStr"/>
-      <c r="AG5" s="4" t="inlineStr"/>
-      <c r="AH5" s="4" t="inlineStr"/>
-      <c r="AI5" s="4" t="inlineStr"/>
-      <c r="AJ5" s="4" t="inlineStr"/>
-      <c r="AK5" s="4" t="inlineStr"/>
-      <c r="AL5" s="4" t="inlineStr"/>
-      <c r="AM5" s="4" t="inlineStr"/>
-      <c r="AN5" s="4" t="inlineStr"/>
-      <c r="AO5" s="4" t="inlineStr">
+      <c r="AE5" s="3" t="inlineStr"/>
+      <c r="AF5" s="3" t="inlineStr"/>
+      <c r="AG5" s="3" t="inlineStr"/>
+      <c r="AH5" s="3" t="inlineStr"/>
+      <c r="AI5" s="3" t="inlineStr"/>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" s="3" t="inlineStr"/>
+      <c r="AM5" s="3" t="inlineStr"/>
+      <c r="AN5" s="3" t="inlineStr"/>
+      <c r="AO5" s="3" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AP5" s="4" t="inlineStr"/>
-      <c r="AQ5" s="4" t="inlineStr"/>
-      <c r="AR5" s="4" t="inlineStr"/>
-      <c r="AS5" s="4" t="inlineStr"/>
-      <c r="AT5" s="4" t="inlineStr"/>
-      <c r="AU5" s="4" t="inlineStr"/>
-      <c r="AV5" s="4" t="inlineStr"/>
-      <c r="AW5" s="4" t="inlineStr"/>
-      <c r="AX5" s="4" t="inlineStr"/>
-      <c r="AY5" s="4" t="inlineStr"/>
-      <c r="AZ5" s="4" t="inlineStr"/>
-      <c r="BA5" s="4" t="inlineStr"/>
-      <c r="BB5" s="4" t="inlineStr">
+      <c r="AP5" s="3" t="inlineStr"/>
+      <c r="AQ5" s="3" t="inlineStr"/>
+      <c r="AR5" s="3" t="inlineStr"/>
+      <c r="AS5" s="3" t="inlineStr"/>
+      <c r="AT5" s="3" t="inlineStr"/>
+      <c r="AU5" s="3" t="inlineStr"/>
+      <c r="AV5" s="3" t="inlineStr"/>
+      <c r="AW5" s="3" t="inlineStr"/>
+      <c r="AX5" s="3" t="inlineStr"/>
+      <c r="AY5" s="3" t="inlineStr"/>
+      <c r="AZ5" s="3" t="inlineStr"/>
+      <c r="BA5" s="3" t="inlineStr"/>
+      <c r="BB5" s="3" t="inlineStr">
         <is>
           <t>COR</t>
         </is>
       </c>
-      <c r="BC5" s="4" t="inlineStr">
+      <c r="BC5" s="3" t="inlineStr">
         <is>
           <t>主體證據不足</t>
         </is>
       </c>
-      <c r="BD5" s="4" t="inlineStr">
+      <c r="BD5" s="3" t="inlineStr">
         <is>
           <t>COR</t>
         </is>
       </c>
-      <c r="BE5" s="4" t="inlineStr">
+      <c r="BE5" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF5" s="4" t="inlineStr">
+      <c r="BF5" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG5" s="4" t="inlineStr"/>
-      <c r="BH5" s="4" t="inlineStr"/>
+      <c r="BG5" s="3" t="inlineStr"/>
+      <c r="BH5" s="3" t="inlineStr"/>
+      <c r="BI5" s="3" t="inlineStr"/>
+      <c r="BJ5" s="3" t="inlineStr"/>
+      <c r="BK5" s="3" t="inlineStr"/>
+      <c r="BL5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr"/>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr"/>
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>ServiceNow</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>2026-08-18T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>Wildfires and extreme heat show climate change is now Europe’s biggest security threat</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>天災</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr">
+      <c r="K6" s="3" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L6" s="4" t="inlineStr">
+      <c r="L6" s="3" t="inlineStr">
         <is>
           <t>待人工覆核</t>
         </is>
       </c>
-      <c r="M6" s="4" t="inlineStr">
+      <c r="M6" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="N6" s="3" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O6" s="4" t="inlineStr">
+      <c r="O6" s="3" t="inlineStr">
         <is>
           <t>'-0.117</t>
         </is>
       </c>
-      <c r="P6" s="4" t="inlineStr"/>
-      <c r="Q6" s="4" t="inlineStr"/>
-      <c r="R6" s="4" t="inlineStr"/>
-      <c r="S6" s="4" t="inlineStr"/>
-      <c r="T6" s="4" t="inlineStr">
+      <c r="P6" s="3" t="inlineStr"/>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr"/>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr">
         <is>
           <t>主體證據不足</t>
         </is>
       </c>
-      <c r="U6" s="4" t="inlineStr">
+      <c r="U6" s="3" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNVVV4eTNJanNDd1JqdUd6MUtINkQ1bXdaS1czelZ1OF9wdmRrZFdpR3hQU3l1aTV5RFpoUVg1bzVuTEY1Zm1Ic21Md2U2NzR3YS1GU21VRHNyemhCRTAxVTR4dmdyWTYtN1FrbzZDZXBfOElBdDd4aktsOS1aMGRXMFFZaFpEcS1sYVp5enJMMFRDTTJCY0w5bE41Wk5vdVREUGQ2Vm5vMl9pNU5KR05LUTRvSENsQnJGQXdB?oc=5</t>
         </is>
       </c>
-      <c r="V6" s="4" t="inlineStr">
+      <c r="V6" s="3" t="inlineStr">
         <is>
           <t>Chatham House</t>
         </is>
       </c>
-      <c r="W6" s="4" t="inlineStr"/>
-      <c r="X6" s="4" t="inlineStr">
+      <c r="W6" s="3" t="inlineStr"/>
+      <c r="X6" s="3" t="inlineStr">
         <is>
           <t>OPERATIONS</t>
         </is>
       </c>
-      <c r="Y6" s="4" t="inlineStr">
+      <c r="Y6" s="3" t="inlineStr">
         <is>
           <t>NATURAL_DISASTER</t>
         </is>
       </c>
-      <c r="Z6" s="4" t="inlineStr">
+      <c r="Z6" s="3" t="inlineStr">
         <is>
           <t>wildfire</t>
         </is>
       </c>
-      <c r="AA6" s="4" t="inlineStr">
+      <c r="AA6" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB6" s="4" t="inlineStr"/>
-      <c r="AC6" s="4" t="inlineStr">
+      <c r="AB6" s="3" t="inlineStr"/>
+      <c r="AC6" s="3" t="inlineStr">
         <is>
           <t>46b57714c7435eb30433a2e4</t>
         </is>
       </c>
-      <c r="AD6" s="4" t="inlineStr">
+      <c r="AD6" s="3" t="inlineStr">
         <is>
           <t>584d67c4f9af2372ea1714ff</t>
         </is>
       </c>
-      <c r="AE6" s="4" t="inlineStr"/>
-      <c r="AF6" s="4" t="inlineStr"/>
-      <c r="AG6" s="4" t="inlineStr"/>
-      <c r="AH6" s="4" t="inlineStr"/>
-      <c r="AI6" s="4" t="inlineStr"/>
-      <c r="AJ6" s="4" t="inlineStr"/>
-      <c r="AK6" s="4" t="inlineStr"/>
-      <c r="AL6" s="4" t="inlineStr"/>
-      <c r="AM6" s="4" t="inlineStr"/>
-      <c r="AN6" s="4" t="inlineStr"/>
-      <c r="AO6" s="4" t="inlineStr">
+      <c r="AE6" s="3" t="inlineStr"/>
+      <c r="AF6" s="3" t="inlineStr"/>
+      <c r="AG6" s="3" t="inlineStr"/>
+      <c r="AH6" s="3" t="inlineStr"/>
+      <c r="AI6" s="3" t="inlineStr"/>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr"/>
+      <c r="AM6" s="3" t="inlineStr"/>
+      <c r="AN6" s="3" t="inlineStr"/>
+      <c r="AO6" s="3" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AP6" s="4" t="inlineStr"/>
-      <c r="AQ6" s="4" t="inlineStr"/>
-      <c r="AR6" s="4" t="inlineStr"/>
-      <c r="AS6" s="4" t="inlineStr"/>
-      <c r="AT6" s="4" t="inlineStr"/>
-      <c r="AU6" s="4" t="inlineStr"/>
-      <c r="AV6" s="4" t="inlineStr"/>
-      <c r="AW6" s="4" t="inlineStr"/>
-      <c r="AX6" s="4" t="inlineStr"/>
-      <c r="AY6" s="4" t="inlineStr"/>
-      <c r="AZ6" s="4" t="inlineStr"/>
-      <c r="BA6" s="4" t="inlineStr"/>
-      <c r="BB6" s="4" t="inlineStr">
+      <c r="AP6" s="3" t="inlineStr"/>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr"/>
+      <c r="AS6" s="3" t="inlineStr"/>
+      <c r="AT6" s="3" t="inlineStr"/>
+      <c r="AU6" s="3" t="inlineStr"/>
+      <c r="AV6" s="3" t="inlineStr"/>
+      <c r="AW6" s="3" t="inlineStr"/>
+      <c r="AX6" s="3" t="inlineStr"/>
+      <c r="AY6" s="3" t="inlineStr"/>
+      <c r="AZ6" s="3" t="inlineStr"/>
+      <c r="BA6" s="3" t="inlineStr"/>
+      <c r="BB6" s="3" t="inlineStr">
         <is>
           <t>NOW</t>
         </is>
       </c>
-      <c r="BC6" s="4" t="inlineStr">
+      <c r="BC6" s="3" t="inlineStr">
         <is>
           <t>主體證據不足</t>
         </is>
       </c>
-      <c r="BD6" s="4" t="inlineStr">
+      <c r="BD6" s="3" t="inlineStr">
         <is>
           <t>NOW</t>
         </is>
       </c>
-      <c r="BE6" s="4" t="inlineStr">
+      <c r="BE6" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF6" s="4" t="inlineStr">
+      <c r="BF6" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG6" s="4" t="inlineStr"/>
-      <c r="BH6" s="4" t="inlineStr"/>
+      <c r="BG6" s="3" t="inlineStr"/>
+      <c r="BH6" s="3" t="inlineStr"/>
+      <c r="BI6" s="3" t="inlineStr"/>
+      <c r="BJ6" s="3" t="inlineStr"/>
+      <c r="BK6" s="3" t="inlineStr"/>
+      <c r="BL6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>NVR</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>NVR, Inc. Common Stock</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>2026-08-18T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>NVR (NVR) EPS and Revenue Review: EPS Falls Short of Its Estimate under the Current Snapshot; Shares Fall 0.42% - Earnings Season Review</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr"/>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>股價下跌</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr">
+      <c r="K7" s="3" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L7" s="4" t="inlineStr"/>
-      <c r="M7" s="4" t="inlineStr">
+      <c r="L7" s="3" t="inlineStr"/>
+      <c r="M7" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N7" s="4" t="inlineStr">
+      <c r="N7" s="3" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O7" s="4" t="inlineStr">
+      <c r="O7" s="3" t="inlineStr">
         <is>
           <t>'-0.964</t>
         </is>
       </c>
-      <c r="P7" s="4" t="inlineStr"/>
-      <c r="Q7" s="4" t="inlineStr"/>
-      <c r="R7" s="4" t="inlineStr"/>
-      <c r="S7" s="4" t="inlineStr"/>
-      <c r="T7" s="4" t="inlineStr">
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr"/>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U7" s="4" t="inlineStr">
+      <c r="U7" s="3" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxPVUhxNHZ0ZXc1Q1hoYmpSYUt4ZnZnNlFRRDVUdWprbVViaFNmdGNRZ21qTEl1bWZtUVhYeS01bUZZc001b3R2WjRsMnRLN0hWMGNlY2ZMMkNIYXdnMGRhQ0FTVkhnNXZJb09NQjBHRC1oekctNHUtR0MyQnQzWjQzU2ZKd010Y1dGNkktbktfUXNMNS1yNnVfR1hlaEJGUVRIdEFDaXdPSDBaR1l6Z3RmY0RPQTRHdlkzRFM1VG8zVDBmY2FsRmVrMEZPOHVUT2dneDYyVnFJeE1JYk1Vb3hwQVV4Y0w?oc=5</t>
         </is>
       </c>
-      <c r="V7" s="4" t="inlineStr">
+      <c r="V7" s="3" t="inlineStr">
         <is>
           <t>dars.gov.et</t>
         </is>
       </c>
-      <c r="W7" s="4" t="inlineStr"/>
-      <c r="X7" s="4" t="inlineStr">
+      <c r="W7" s="3" t="inlineStr"/>
+      <c r="X7" s="3" t="inlineStr">
         <is>
           <t>MARKET</t>
         </is>
       </c>
-      <c r="Y7" s="4" t="inlineStr">
+      <c r="Y7" s="3" t="inlineStr">
         <is>
           <t>PRICE_MOVEMENT</t>
         </is>
       </c>
-      <c r="Z7" s="4" t="inlineStr">
+      <c r="Z7" s="3" t="inlineStr">
         <is>
           <t>shares fall</t>
         </is>
       </c>
-      <c r="AA7" s="4" t="inlineStr">
+      <c r="AA7" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB7" s="4" t="inlineStr"/>
-      <c r="AC7" s="4" t="inlineStr">
+      <c r="AB7" s="3" t="inlineStr"/>
+      <c r="AC7" s="3" t="inlineStr">
         <is>
           <t>aea408fe3f0396b31a2d526d</t>
         </is>
       </c>
-      <c r="AD7" s="4" t="inlineStr">
+      <c r="AD7" s="3" t="inlineStr">
         <is>
           <t>03578736f23403259ada2d65</t>
         </is>
       </c>
-      <c r="AE7" s="4" t="inlineStr"/>
-      <c r="AF7" s="4" t="inlineStr"/>
-      <c r="AG7" s="4" t="inlineStr"/>
-      <c r="AH7" s="4" t="inlineStr"/>
-      <c r="AI7" s="4" t="inlineStr"/>
-      <c r="AJ7" s="4" t="inlineStr"/>
-      <c r="AK7" s="4" t="inlineStr"/>
-      <c r="AL7" s="4" t="inlineStr"/>
-      <c r="AM7" s="4" t="inlineStr"/>
-      <c r="AN7" s="4" t="inlineStr"/>
-      <c r="AO7" s="4" t="inlineStr"/>
-      <c r="AP7" s="4" t="inlineStr"/>
-      <c r="AQ7" s="4" t="inlineStr"/>
-      <c r="AR7" s="4" t="inlineStr"/>
-      <c r="AS7" s="4" t="inlineStr"/>
-      <c r="AT7" s="4" t="inlineStr"/>
-      <c r="AU7" s="4" t="inlineStr"/>
-      <c r="AV7" s="4" t="inlineStr"/>
-      <c r="AW7" s="4" t="inlineStr">
+      <c r="AE7" s="3" t="inlineStr"/>
+      <c r="AF7" s="3" t="inlineStr"/>
+      <c r="AG7" s="3" t="inlineStr"/>
+      <c r="AH7" s="3" t="inlineStr"/>
+      <c r="AI7" s="3" t="inlineStr"/>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" s="3" t="inlineStr"/>
+      <c r="AM7" s="3" t="inlineStr"/>
+      <c r="AN7" s="3" t="inlineStr"/>
+      <c r="AO7" s="3" t="inlineStr"/>
+      <c r="AP7" s="3" t="inlineStr"/>
+      <c r="AQ7" s="3" t="inlineStr"/>
+      <c r="AR7" s="3" t="inlineStr"/>
+      <c r="AS7" s="3" t="inlineStr"/>
+      <c r="AT7" s="3" t="inlineStr"/>
+      <c r="AU7" s="3" t="inlineStr"/>
+      <c r="AV7" s="3" t="inlineStr"/>
+      <c r="AW7" s="3" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX7" s="4" t="inlineStr"/>
-      <c r="AY7" s="4" t="inlineStr"/>
-      <c r="AZ7" s="4" t="inlineStr"/>
-      <c r="BA7" s="4" t="inlineStr"/>
-      <c r="BB7" s="4" t="inlineStr">
+      <c r="AX7" s="3" t="inlineStr"/>
+      <c r="AY7" s="3" t="inlineStr"/>
+      <c r="AZ7" s="3" t="inlineStr"/>
+      <c r="BA7" s="3" t="inlineStr"/>
+      <c r="BB7" s="3" t="inlineStr">
         <is>
           <t>NVR</t>
         </is>
       </c>
-      <c r="BC7" s="4" t="inlineStr">
+      <c r="BC7" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD7" s="4" t="inlineStr"/>
-      <c r="BE7" s="4" t="inlineStr">
+      <c r="BD7" s="3" t="inlineStr"/>
+      <c r="BE7" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF7" s="4" t="inlineStr">
+      <c r="BF7" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG7" s="4" t="inlineStr">
+      <c r="BG7" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH7" s="4" t="inlineStr"/>
+      <c r="BH7" s="3" t="inlineStr"/>
+      <c r="BI7" s="3" t="inlineStr"/>
+      <c r="BJ7" s="3" t="inlineStr"/>
+      <c r="BK7" s="3" t="inlineStr"/>
+      <c r="BL7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1911,13 +1995,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1970,7 +2058,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>9a9125f74f8d4c9c8e67ab3610d83d93</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
           <t>6ac6fca41805ccc7fbe440cd</t>
@@ -1991,7 +2083,11 @@
       <c r="AL8" s="2" t="inlineStr"/>
       <c r="AM8" s="2" t="inlineStr"/>
       <c r="AN8" s="2" t="inlineStr"/>
-      <c r="AO8" s="2" t="inlineStr"/>
+      <c r="AO8" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP8" s="2" t="inlineStr"/>
       <c r="AQ8" s="2" t="inlineStr"/>
       <c r="AR8" s="2" t="inlineStr"/>
@@ -2027,180 +2123,220 @@
         </is>
       </c>
       <c r="BH8" s="2" t="inlineStr"/>
+      <c r="BI8" s="2" t="inlineStr"/>
+      <c r="BJ8" s="2" t="inlineStr"/>
+      <c r="BK8" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>ICE</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Intercontinental Exchange Inc. Common Stock</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>2026-08-18T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>Minnesota attorney general sues Texas governor to compel ICE agent’s extradition for trial</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>'-0.886</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr"/>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr"/>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNalRFZW9SYUlfeVpYRXU5ZWEyRW9Fb1ZEb0FnYU1vNnVOT3NKdS1qVGJCNEx6Nzc5aTgwQ2lCYTQtUDU3emNtRGRpRXJZbEptSUZIQnVrbzBfMmllaW8xa25JUVlNd0lFRXpLenB0WVotU2F6aEI2eDdVclQ4TXRmMDFOV0ZfUVJSZGlxUEpuYjZzSElIX0Z5ZVV3UGJyQUhNRENGMWEwSGRQdUFEWHE4S3kySFdYaFMx?oc=5</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>NBC News</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr"/>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>attorney general</t>
+        </is>
+      </c>
+      <c r="AA9" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>e826f67f91634fd0bd269280bba01b27</t>
+        </is>
+      </c>
+      <c r="AC9" s="3" t="inlineStr">
+        <is>
+          <t>dae1a4662d14e47c8f439382</t>
+        </is>
+      </c>
+      <c r="AD9" s="3" t="inlineStr">
+        <is>
+          <t>016d51d5631e9130d8acf040</t>
+        </is>
+      </c>
+      <c r="AE9" s="3" t="inlineStr"/>
+      <c r="AF9" s="3" t="inlineStr"/>
+      <c r="AG9" s="3" t="inlineStr"/>
+      <c r="AH9" s="3" t="inlineStr"/>
+      <c r="AI9" s="3" t="inlineStr"/>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" s="3" t="inlineStr"/>
+      <c r="AM9" s="3" t="inlineStr"/>
+      <c r="AN9" s="3" t="inlineStr"/>
+      <c r="AO9" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>'-0.886</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr"/>
-      <c r="Q9" s="2" t="inlineStr"/>
-      <c r="R9" s="2" t="inlineStr"/>
-      <c r="S9" s="2" t="inlineStr"/>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNalRFZW9SYUlfeVpYRXU5ZWEyRW9Fb1ZEb0FnYU1vNnVOT3NKdS1qVGJCNEx6Nzc5aTgwQ2lCYTQtUDU3emNtRGRpRXJZbEptSUZIQnVrbzBfMmllaW8xa25JUVlNd0lFRXpLenB0WVotU2F6aEI2eDdVclQ4TXRmMDFOV0ZfUVJSZGlxUEpuYjZzSElIX0Z5ZVV3UGJyQUhNRENGMWEwSGRQdUFEWHE4S3kySFdYaFMx?oc=5</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>NBC News</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr"/>
-      <c r="X9" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y9" s="2" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z9" s="2" t="inlineStr">
-        <is>
-          <t>attorney general</t>
-        </is>
-      </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
-      <c r="AC9" s="2" t="inlineStr">
-        <is>
-          <t>dae1a4662d14e47c8f439382</t>
-        </is>
-      </c>
-      <c r="AD9" s="2" t="inlineStr">
-        <is>
-          <t>016d51d5631e9130d8acf040</t>
-        </is>
-      </c>
-      <c r="AE9" s="2" t="inlineStr"/>
-      <c r="AF9" s="2" t="inlineStr"/>
-      <c r="AG9" s="2" t="inlineStr"/>
-      <c r="AH9" s="2" t="inlineStr"/>
-      <c r="AI9" s="2" t="inlineStr"/>
-      <c r="AJ9" s="2" t="inlineStr"/>
-      <c r="AK9" s="2" t="inlineStr"/>
-      <c r="AL9" s="2" t="inlineStr"/>
-      <c r="AM9" s="2" t="inlineStr"/>
-      <c r="AN9" s="2" t="inlineStr"/>
-      <c r="AO9" s="2" t="inlineStr"/>
-      <c r="AP9" s="2" t="inlineStr"/>
-      <c r="AQ9" s="2" t="inlineStr"/>
-      <c r="AR9" s="2" t="inlineStr"/>
-      <c r="AS9" s="2" t="inlineStr"/>
-      <c r="AT9" s="2" t="inlineStr"/>
-      <c r="AU9" s="2" t="inlineStr"/>
-      <c r="AV9" s="2" t="inlineStr"/>
-      <c r="AW9" s="2" t="inlineStr">
+      <c r="AP9" s="3" t="inlineStr"/>
+      <c r="AQ9" s="3" t="inlineStr"/>
+      <c r="AR9" s="3" t="inlineStr"/>
+      <c r="AS9" s="3" t="inlineStr"/>
+      <c r="AT9" s="3" t="inlineStr"/>
+      <c r="AU9" s="3" t="inlineStr"/>
+      <c r="AV9" s="3" t="inlineStr"/>
+      <c r="AW9" s="3" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX9" s="2" t="inlineStr"/>
-      <c r="AY9" s="2" t="inlineStr"/>
-      <c r="AZ9" s="2" t="inlineStr"/>
-      <c r="BA9" s="2" t="inlineStr"/>
-      <c r="BB9" s="2" t="inlineStr">
+      <c r="AX9" s="3" t="inlineStr"/>
+      <c r="AY9" s="3" t="inlineStr"/>
+      <c r="AZ9" s="3" t="inlineStr"/>
+      <c r="BA9" s="3" t="inlineStr"/>
+      <c r="BB9" s="3" t="inlineStr">
         <is>
           <t>ICE</t>
         </is>
       </c>
-      <c r="BC9" s="2" t="inlineStr">
+      <c r="BC9" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD9" s="2" t="inlineStr"/>
-      <c r="BE9" s="2" t="inlineStr">
+      <c r="BD9" s="3" t="inlineStr"/>
+      <c r="BE9" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF9" s="2" t="inlineStr">
+      <c r="BF9" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG9" s="2" t="inlineStr">
+      <c r="BG9" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH9" s="2" t="inlineStr"/>
+      <c r="BH9" s="3" t="inlineStr"/>
+      <c r="BI9" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ9" s="3" t="inlineStr"/>
+      <c r="BK9" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL9" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2251,13 +2387,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -2310,7 +2450,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>8946e078a3e44b2b8f98ddbad196b514</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
           <t>6a8884a14443cde81b9bbbe4</t>
@@ -2331,7 +2475,11 @@
       <c r="AL10" s="2" t="inlineStr"/>
       <c r="AM10" s="2" t="inlineStr"/>
       <c r="AN10" s="2" t="inlineStr"/>
-      <c r="AO10" s="2" t="inlineStr"/>
+      <c r="AO10" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP10" s="2" t="inlineStr"/>
       <c r="AQ10" s="2" t="inlineStr"/>
       <c r="AR10" s="2" t="inlineStr"/>
@@ -2367,9 +2515,21 @@
         </is>
       </c>
       <c r="BH10" s="2" t="inlineStr"/>
+      <c r="BI10" s="2" t="inlineStr"/>
+      <c r="BJ10" s="2" t="inlineStr"/>
+      <c r="BK10" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH10"/>
+  <autoFilter ref="A1:BL10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2380,7 +2540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH6"/>
+  <dimension ref="A1:BL4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2443,6 +2603,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2746,6 +2910,26 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -2758,7 +2942,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr"/>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Walt Disney Company (The)</t>
@@ -2792,17 +2980,17 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -2851,7 +3039,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>32beac2ca3c64d5cab7fe72d730bb172</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>e394e6a4e994de361a644b0f</t>
@@ -2874,7 +3066,7 @@
       <c r="AN2" s="2" t="inlineStr"/>
       <c r="AO2" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP2" s="2" t="inlineStr"/>
@@ -2916,172 +3108,212 @@
       </c>
       <c r="BG2" s="2" t="inlineStr"/>
       <c r="BH2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="BJ2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Kroger</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>PNR</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Pentair</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>2026-08-18T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Ice cream brand sold at Kroger, Walmart and Target files for bankruptcy</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>破產</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>PNR Shareholder Alert: October 2, 2026 Lead Plaintiff Deadline in Pentair plc Securities Class Action - Contact The Gross Law Firm</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>重大訴訟</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、持續追蹤</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr"/>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>'-0.073</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr"/>
+      <c r="Q3" s="2" t="inlineStr"/>
+      <c r="R3" s="2" t="inlineStr"/>
+      <c r="S3" s="2" t="inlineStr"/>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U3" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilgJBVV95cUxPZktiZ2wzc0Npa3pSZTBHbnRVcEMyN01BNTlhLXBZaHlGRWllOHE1a1EzU3BlNEhLcEpoWjBYLUR0SzMwV1pxaTFnZXlQVXBkMUh6N0Fya0h2NkFGQlhEdjVOcWVxZGxfLWRKSWRsMjhzUkFVdjFuNmR2LVc1MXJCWWlnWF9WbnBDc0VBVnc3eTNDZ1ZnWGc2NEh3ZU9UWElPMFRvQzhncmRJQXpPZ0FYYUJoN2hYNzJONDJVZWVhVS0zQjFFMHlScFZYS2hMYnlNcy1NbzRUeV8zZDlLc21ncDJsclluVWFEa1l3QnJ3N19iVkxNYU5NWG4xT1c5Sl9fVlN0bHFzVkxISDI5N2wyNHhMT3VyQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Morningstar</t>
+        </is>
+      </c>
+      <c r="W3" s="2" t="inlineStr"/>
+      <c r="X3" s="2" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y3" s="2" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z3" s="2" t="inlineStr">
+        <is>
+          <t>class action</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>9a9125f74f8d4c9c8e67ab3610d83d93</t>
+        </is>
+      </c>
+      <c r="AC3" s="2" t="inlineStr">
+        <is>
+          <t>6ac6fca41805ccc7fbe440cd</t>
+        </is>
+      </c>
+      <c r="AD3" s="2" t="inlineStr">
+        <is>
+          <t>16c498ebe35f9ed2f4a0d030</t>
+        </is>
+      </c>
+      <c r="AE3" s="2" t="inlineStr"/>
+      <c r="AF3" s="2" t="inlineStr"/>
+      <c r="AG3" s="2" t="inlineStr"/>
+      <c r="AH3" s="2" t="inlineStr"/>
+      <c r="AI3" s="2" t="inlineStr"/>
+      <c r="AJ3" s="2" t="inlineStr"/>
+      <c r="AK3" s="2" t="inlineStr"/>
+      <c r="AL3" s="2" t="inlineStr"/>
+      <c r="AM3" s="2" t="inlineStr"/>
+      <c r="AN3" s="2" t="inlineStr"/>
+      <c r="AO3" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>'-0.781</t>
-        </is>
-      </c>
-      <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="3" t="inlineStr"/>
-      <c r="S3" s="3" t="inlineStr"/>
-      <c r="T3" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U3" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQbS1yRjd5R3FTUzNiUnVaaHBtaVN4ZDY3VmRfWm5IZWpQNU01S0UzRmg0WEFieFc0ei0wX3FEMjA5bGtXeEl5bG5vX09sVFM2TDFYRzNteVd3djhBWHRmdzc1aU0wWUtVdTQxdTJMVk9WXzA0Ni04SWpRdVJ4Q0ZpQXp5V1RRTkx3OFBXR0hZUkFDR21zZEVBOW9pOGIwTWJkUGd2VWFTWE4?oc=5</t>
-        </is>
-      </c>
-      <c r="V3" s="3" t="inlineStr">
-        <is>
-          <t>katu.com</t>
-        </is>
-      </c>
-      <c r="W3" s="3" t="inlineStr"/>
-      <c r="X3" s="3" t="inlineStr">
-        <is>
-          <t>FINANCIAL</t>
-        </is>
-      </c>
-      <c r="Y3" s="3" t="inlineStr">
-        <is>
-          <t>BANKRUPTCY</t>
-        </is>
-      </c>
-      <c r="Z3" s="3" t="inlineStr">
-        <is>
-          <t>bankruptcy</t>
-        </is>
-      </c>
-      <c r="AA3" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="3" t="inlineStr"/>
-      <c r="AC3" s="3" t="inlineStr">
-        <is>
-          <t>5f384da3250c133e5ee2f6b0</t>
-        </is>
-      </c>
-      <c r="AD3" s="3" t="inlineStr">
-        <is>
-          <t>9063606cf67dcb49b5e0ff66</t>
-        </is>
-      </c>
-      <c r="AE3" s="3" t="inlineStr"/>
-      <c r="AF3" s="3" t="inlineStr"/>
-      <c r="AG3" s="3" t="inlineStr"/>
-      <c r="AH3" s="3" t="inlineStr"/>
-      <c r="AI3" s="3" t="inlineStr"/>
-      <c r="AJ3" s="3" t="inlineStr"/>
-      <c r="AK3" s="3" t="inlineStr"/>
-      <c r="AL3" s="3" t="inlineStr"/>
-      <c r="AM3" s="3" t="inlineStr"/>
-      <c r="AN3" s="3" t="inlineStr"/>
-      <c r="AO3" s="3" t="inlineStr"/>
-      <c r="AP3" s="3" t="inlineStr"/>
-      <c r="AQ3" s="3" t="inlineStr"/>
-      <c r="AR3" s="3" t="inlineStr"/>
-      <c r="AS3" s="3" t="inlineStr"/>
-      <c r="AT3" s="3" t="inlineStr"/>
-      <c r="AU3" s="3" t="inlineStr"/>
-      <c r="AV3" s="3" t="inlineStr"/>
-      <c r="AW3" s="3" t="inlineStr"/>
-      <c r="AX3" s="3" t="inlineStr"/>
-      <c r="AY3" s="3" t="inlineStr"/>
-      <c r="AZ3" s="3" t="inlineStr"/>
-      <c r="BA3" s="3" t="inlineStr"/>
-      <c r="BB3" s="3" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="BC3" s="3" t="inlineStr">
+      <c r="AP3" s="2" t="inlineStr"/>
+      <c r="AQ3" s="2" t="inlineStr"/>
+      <c r="AR3" s="2" t="inlineStr"/>
+      <c r="AS3" s="2" t="inlineStr"/>
+      <c r="AT3" s="2" t="inlineStr"/>
+      <c r="AU3" s="2" t="inlineStr"/>
+      <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" s="2" t="inlineStr"/>
+      <c r="AX3" s="2" t="inlineStr"/>
+      <c r="AY3" s="2" t="inlineStr"/>
+      <c r="AZ3" s="2" t="inlineStr"/>
+      <c r="BA3" s="2" t="inlineStr"/>
+      <c r="BB3" s="2" t="inlineStr">
+        <is>
+          <t>PNR</t>
+        </is>
+      </c>
+      <c r="BC3" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD3" s="3" t="inlineStr"/>
-      <c r="BE3" s="3" t="inlineStr">
+      <c r="BD3" s="2" t="inlineStr"/>
+      <c r="BE3" s="2" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF3" s="3" t="inlineStr"/>
-      <c r="BG3" s="3" t="inlineStr">
+      <c r="BF3" s="2" t="inlineStr"/>
+      <c r="BG3" s="2" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH3" s="3" t="inlineStr"/>
+      <c r="BH3" s="2" t="inlineStr"/>
+      <c r="BI3" s="2" t="inlineStr"/>
+      <c r="BJ3" s="2" t="inlineStr"/>
+      <c r="BK3" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -3096,12 +3328,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>PNR</t>
+          <t>LHX</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Pentair</t>
+          <t>L3Harris</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -3111,7 +3343,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>PNR Shareholder Alert: October 2, 2026 Lead Plaintiff Deadline in Pentair plc Securities Class Action - Contact The Gross Law Firm</t>
+          <t>L3Harris fires Kubasik for repeating the misconduct that cost him Lockheed Martin</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
@@ -3122,7 +3354,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>重大訴訟</t>
+          <t>高管不當行為</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3132,13 +3364,17 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3148,7 +3384,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>'-0.073</t>
+          <t>'-0.928</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr"/>
@@ -3162,28 +3398,28 @@
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgJBVV95cUxPZktiZ2wzc0Npa3pSZTBHbnRVcEMyN01BNTlhLXBZaHlGRWllOHE1a1EzU3BlNEhLcEpoWjBYLUR0SzMwV1pxaTFnZXlQVXBkMUh6N0Fya0h2NkFGQlhEdjVOcWVxZGxfLWRKSWRsMjhzUkFVdjFuNmR2LVc1MXJCWWlnWF9WbnBDc0VBVnc3eTNDZ1ZnWGc2NEh3ZU9UWElPMFRvQzhncmRJQXpPZ0FYYUJoN2hYNzJONDJVZWVhVS0zQjFFMHlScFZYS2hMYnlNcy1NbzRUeV8zZDlLc21ncDJsclluVWFEa1l3QnJ3N19iVkxNYU5NWG4xT1c5Sl9fVlN0bHFzVkxISDI5N2wyNHhMT3VyQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTFBUYUxyQkp4clFrV1h2NXBtZVhuQ3k3Qk5IeDduVkEtb2M4QXJ1ZGRYY0UxTG01NDduQUZFdW84V1lLZjQ2alpSZzFmajNXZ3JIc25HRkp0MWcyd1Q3bDBWSnNrbFRGLTBPTnIwdW9pZW9EcFhwX1E?oc=5</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Morningstar</t>
+          <t>Martin Cid Magazine</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr"/>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>LEGAL</t>
+          <t>GOVERNANCE</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>MAJOR_LITIGATION</t>
+          <t>EXECUTIVE_MISCONDUCT</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>class action</t>
+          <t>misconduct</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -3191,15 +3427,19 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>8946e078a3e44b2b8f98ddbad196b514</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6ac6fca41805ccc7fbe440cd</t>
+          <t>6a8884a14443cde81b9bbbe4</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>16c498ebe35f9ed2f4a0d030</t>
+          <t>b60049fda40dcd154e05fb75</t>
         </is>
       </c>
       <c r="AE4" s="2" t="inlineStr"/>
@@ -3212,7 +3452,11 @@
       <c r="AL4" s="2" t="inlineStr"/>
       <c r="AM4" s="2" t="inlineStr"/>
       <c r="AN4" s="2" t="inlineStr"/>
-      <c r="AO4" s="2" t="inlineStr"/>
+      <c r="AO4" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP4" s="2" t="inlineStr"/>
       <c r="AQ4" s="2" t="inlineStr"/>
       <c r="AR4" s="2" t="inlineStr"/>
@@ -3227,7 +3471,7 @@
       <c r="BA4" s="2" t="inlineStr"/>
       <c r="BB4" s="2" t="inlineStr">
         <is>
-          <t>PNR</t>
+          <t>LHX</t>
         </is>
       </c>
       <c r="BC4" s="2" t="inlineStr">
@@ -3248,349 +3492,21 @@
         </is>
       </c>
       <c r="BH4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>ICE</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Intercontinental Exchange Inc. Common Stock</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-18T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Minnesota attorney general sues Texas governor to compel ICE agent’s extradition for trial</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>'-0.886</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr"/>
-      <c r="Q5" s="2" t="inlineStr"/>
-      <c r="R5" s="2" t="inlineStr"/>
-      <c r="S5" s="2" t="inlineStr"/>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNalRFZW9SYUlfeVpYRXU5ZWEyRW9Fb1ZEb0FnYU1vNnVOT3NKdS1qVGJCNEx6Nzc5aTgwQ2lCYTQtUDU3emNtRGRpRXJZbEptSUZIQnVrbzBfMmllaW8xa25JUVlNd0lFRXpLenB0WVotU2F6aEI2eDdVclQ4TXRmMDFOV0ZfUVJSZGlxUEpuYjZzSElIX0Z5ZVV3UGJyQUhNRENGMWEwSGRQdUFEWHE4S3kySFdYaFMx?oc=5</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>NBC News</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr"/>
-      <c r="X5" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y5" s="2" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z5" s="2" t="inlineStr">
-        <is>
-          <t>attorney general</t>
-        </is>
-      </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
-      <c r="AC5" s="2" t="inlineStr">
-        <is>
-          <t>dae1a4662d14e47c8f439382</t>
-        </is>
-      </c>
-      <c r="AD5" s="2" t="inlineStr">
-        <is>
-          <t>016d51d5631e9130d8acf040</t>
-        </is>
-      </c>
-      <c r="AE5" s="2" t="inlineStr"/>
-      <c r="AF5" s="2" t="inlineStr"/>
-      <c r="AG5" s="2" t="inlineStr"/>
-      <c r="AH5" s="2" t="inlineStr"/>
-      <c r="AI5" s="2" t="inlineStr"/>
-      <c r="AJ5" s="2" t="inlineStr"/>
-      <c r="AK5" s="2" t="inlineStr"/>
-      <c r="AL5" s="2" t="inlineStr"/>
-      <c r="AM5" s="2" t="inlineStr"/>
-      <c r="AN5" s="2" t="inlineStr"/>
-      <c r="AO5" s="2" t="inlineStr"/>
-      <c r="AP5" s="2" t="inlineStr"/>
-      <c r="AQ5" s="2" t="inlineStr"/>
-      <c r="AR5" s="2" t="inlineStr"/>
-      <c r="AS5" s="2" t="inlineStr"/>
-      <c r="AT5" s="2" t="inlineStr"/>
-      <c r="AU5" s="2" t="inlineStr"/>
-      <c r="AV5" s="2" t="inlineStr"/>
-      <c r="AW5" s="2" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX5" s="2" t="inlineStr"/>
-      <c r="AY5" s="2" t="inlineStr"/>
-      <c r="AZ5" s="2" t="inlineStr"/>
-      <c r="BA5" s="2" t="inlineStr"/>
-      <c r="BB5" s="2" t="inlineStr">
-        <is>
-          <t>ICE</t>
-        </is>
-      </c>
-      <c r="BC5" s="2" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD5" s="2" t="inlineStr"/>
-      <c r="BE5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG5" s="2" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>LHX</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>L3Harris</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-18T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>L3Harris fires Kubasik for repeating the misconduct that cost him Lockheed Martin</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>高管不當行為</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>'-0.928</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr"/>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr"/>
-      <c r="S6" s="2" t="inlineStr"/>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTFBUYUxyQkp4clFrV1h2NXBtZVhuQ3k3Qk5IeDduVkEtb2M4QXJ1ZGRYY0UxTG01NDduQUZFdW84V1lLZjQ2alpSZzFmajNXZ3JIc25HRkp0MWcyd1Q3bDBWSnNrbFRGLTBPTnIwdW9pZW9EcFhwX1E?oc=5</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Martin Cid Magazine</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr"/>
-      <c r="X6" s="2" t="inlineStr">
-        <is>
-          <t>GOVERNANCE</t>
-        </is>
-      </c>
-      <c r="Y6" s="2" t="inlineStr">
-        <is>
-          <t>EXECUTIVE_MISCONDUCT</t>
-        </is>
-      </c>
-      <c r="Z6" s="2" t="inlineStr">
-        <is>
-          <t>misconduct</t>
-        </is>
-      </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
-      <c r="AC6" s="2" t="inlineStr">
-        <is>
-          <t>6a8884a14443cde81b9bbbe4</t>
-        </is>
-      </c>
-      <c r="AD6" s="2" t="inlineStr">
-        <is>
-          <t>b60049fda40dcd154e05fb75</t>
-        </is>
-      </c>
-      <c r="AE6" s="2" t="inlineStr"/>
-      <c r="AF6" s="2" t="inlineStr"/>
-      <c r="AG6" s="2" t="inlineStr"/>
-      <c r="AH6" s="2" t="inlineStr"/>
-      <c r="AI6" s="2" t="inlineStr"/>
-      <c r="AJ6" s="2" t="inlineStr"/>
-      <c r="AK6" s="2" t="inlineStr"/>
-      <c r="AL6" s="2" t="inlineStr"/>
-      <c r="AM6" s="2" t="inlineStr"/>
-      <c r="AN6" s="2" t="inlineStr"/>
-      <c r="AO6" s="2" t="inlineStr"/>
-      <c r="AP6" s="2" t="inlineStr"/>
-      <c r="AQ6" s="2" t="inlineStr"/>
-      <c r="AR6" s="2" t="inlineStr"/>
-      <c r="AS6" s="2" t="inlineStr"/>
-      <c r="AT6" s="2" t="inlineStr"/>
-      <c r="AU6" s="2" t="inlineStr"/>
-      <c r="AV6" s="2" t="inlineStr"/>
-      <c r="AW6" s="2" t="inlineStr"/>
-      <c r="AX6" s="2" t="inlineStr"/>
-      <c r="AY6" s="2" t="inlineStr"/>
-      <c r="AZ6" s="2" t="inlineStr"/>
-      <c r="BA6" s="2" t="inlineStr"/>
-      <c r="BB6" s="2" t="inlineStr">
-        <is>
-          <t>LHX</t>
-        </is>
-      </c>
-      <c r="BC6" s="2" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD6" s="2" t="inlineStr"/>
-      <c r="BE6" s="2" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF6" s="2" t="inlineStr"/>
-      <c r="BG6" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH6" s="2" t="inlineStr"/>
+      <c r="BI4" s="2" t="inlineStr"/>
+      <c r="BJ4" s="2" t="inlineStr"/>
+      <c r="BK4" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH6"/>
+  <autoFilter ref="A1:BL4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3601,7 +3517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH4"/>
+  <dimension ref="A1:BL3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3664,6 +3580,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3967,527 +3887,385 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Walt Disney Company (The)</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-18T21:18:09+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>迪士尼旗下ABC起訴美國聯邦通信委員會，指其部分監管行為違法</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr"/>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Cencora</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-18T15:00:00+08:00</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>What: Public Safety Patrol When: August 19, 2026 1003H Where: Bluementritt cor. España Blvd. Status: Negative for flooded area as of 1003H Unit: DMAX3 T.O: B. Mendoza Crew: B. Santos (Source: Manila City DRRM Department) #ManilaPIO #AlertoManile</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>天災</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>僅紀錄</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
         <is>
           <t>待人工覆核</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr"/>
-      <c r="T2" s="2" t="inlineStr">
+      <c r="O2" s="3" t="inlineStr">
+        <is>
+          <t>'-0.108</t>
+        </is>
+      </c>
+      <c r="P2" s="3" t="inlineStr"/>
+      <c r="Q2" s="3" t="inlineStr"/>
+      <c r="R2" s="3" t="inlineStr"/>
+      <c r="S2" s="3" t="inlineStr"/>
+      <c r="T2" s="3" t="inlineStr">
         <is>
           <t>主體證據不足</t>
         </is>
       </c>
-      <c r="U2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.gelonghui.com/live/2618626</t>
-        </is>
-      </c>
-      <c r="V2" s="2" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W2" s="2" t="inlineStr"/>
-      <c r="X2" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y2" s="2" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z2" s="2" t="inlineStr">
-        <is>
-          <t>起訴</t>
-        </is>
-      </c>
-      <c r="AA2" s="2" t="inlineStr">
+      <c r="U2" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxNTXNvREY3UzJxS0ZXNnRQUy1XUGVneThKNTFMc2N6OXV4RGZRcEE3UXJjNzBHU3h1a1NqQnVMMTlRcEFDY3I3eFk3ZUlnVWJURGJUeFNoTjdGTEZ0QmItVlhENVpJMEs0Ymp0Sk5lUlNLNUc1SlNlNW0ybC1jZjR6Z0tiakJFYmMyNGVCenNGTW8tOFVrdGFVOG15NlhURTRNeTktaFM1TVNLWEtIdFVMZDY4UXJtR3p2S0ExZllRbVNTYkQ1djhrX0JpVUJMT1JINmxKUU00R3NCa2E5?oc=5</t>
+        </is>
+      </c>
+      <c r="V2" s="3" t="inlineStr">
+        <is>
+          <t>facebook.com</t>
+        </is>
+      </c>
+      <c r="W2" s="3" t="inlineStr"/>
+      <c r="X2" s="3" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y2" s="3" t="inlineStr">
+        <is>
+          <t>NATURAL_DISASTER</t>
+        </is>
+      </c>
+      <c r="Z2" s="3" t="inlineStr">
+        <is>
+          <t>flood</t>
+        </is>
+      </c>
+      <c r="AA2" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr"/>
-      <c r="AC2" s="2" t="inlineStr">
-        <is>
-          <t>e394e6a4e994de361a644b0f</t>
-        </is>
-      </c>
-      <c r="AD2" s="2" t="inlineStr">
-        <is>
-          <t>22fd0299db8c771718c417da</t>
-        </is>
-      </c>
-      <c r="AE2" s="2" t="inlineStr"/>
-      <c r="AF2" s="2" t="inlineStr"/>
-      <c r="AG2" s="2" t="inlineStr"/>
-      <c r="AH2" s="2" t="inlineStr"/>
-      <c r="AI2" s="2" t="inlineStr"/>
-      <c r="AJ2" s="2" t="inlineStr"/>
-      <c r="AK2" s="2" t="inlineStr"/>
-      <c r="AL2" s="2" t="inlineStr"/>
-      <c r="AM2" s="2" t="inlineStr"/>
-      <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr">
+      <c r="AB2" s="3" t="inlineStr"/>
+      <c r="AC2" s="3" t="inlineStr">
+        <is>
+          <t>304cbada68fbab61665c24fd</t>
+        </is>
+      </c>
+      <c r="AD2" s="3" t="inlineStr">
+        <is>
+          <t>cef13a3c747e25f7c286fb7c</t>
+        </is>
+      </c>
+      <c r="AE2" s="3" t="inlineStr"/>
+      <c r="AF2" s="3" t="inlineStr"/>
+      <c r="AG2" s="3" t="inlineStr"/>
+      <c r="AH2" s="3" t="inlineStr"/>
+      <c r="AI2" s="3" t="inlineStr"/>
+      <c r="AJ2" s="3" t="inlineStr"/>
+      <c r="AK2" s="3" t="inlineStr"/>
+      <c r="AL2" s="3" t="inlineStr"/>
+      <c r="AM2" s="3" t="inlineStr"/>
+      <c r="AN2" s="3" t="inlineStr"/>
+      <c r="AO2" s="3" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AP2" s="2" t="inlineStr"/>
-      <c r="AQ2" s="2" t="inlineStr"/>
-      <c r="AR2" s="2" t="inlineStr"/>
-      <c r="AS2" s="2" t="inlineStr"/>
-      <c r="AT2" s="2" t="inlineStr"/>
-      <c r="AU2" s="2" t="inlineStr"/>
-      <c r="AV2" s="2" t="inlineStr"/>
-      <c r="AW2" s="2" t="inlineStr"/>
-      <c r="AX2" s="2" t="inlineStr"/>
-      <c r="AY2" s="2" t="inlineStr"/>
-      <c r="AZ2" s="2" t="inlineStr"/>
-      <c r="BA2" s="2" t="inlineStr"/>
-      <c r="BB2" s="2" t="inlineStr">
-        <is>
-          <t>DIS</t>
-        </is>
-      </c>
-      <c r="BC2" s="2" t="inlineStr">
+      <c r="AP2" s="3" t="inlineStr"/>
+      <c r="AQ2" s="3" t="inlineStr"/>
+      <c r="AR2" s="3" t="inlineStr"/>
+      <c r="AS2" s="3" t="inlineStr"/>
+      <c r="AT2" s="3" t="inlineStr"/>
+      <c r="AU2" s="3" t="inlineStr"/>
+      <c r="AV2" s="3" t="inlineStr"/>
+      <c r="AW2" s="3" t="inlineStr"/>
+      <c r="AX2" s="3" t="inlineStr"/>
+      <c r="AY2" s="3" t="inlineStr"/>
+      <c r="AZ2" s="3" t="inlineStr"/>
+      <c r="BA2" s="3" t="inlineStr"/>
+      <c r="BB2" s="3" t="inlineStr">
+        <is>
+          <t>COR</t>
+        </is>
+      </c>
+      <c r="BC2" s="3" t="inlineStr">
         <is>
           <t>主體證據不足</t>
         </is>
       </c>
-      <c r="BD2" s="2" t="inlineStr">
-        <is>
-          <t>DIS</t>
-        </is>
-      </c>
-      <c r="BE2" s="2" t="inlineStr">
+      <c r="BD2" s="3" t="inlineStr">
+        <is>
+          <t>COR</t>
+        </is>
+      </c>
+      <c r="BE2" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF2" s="2" t="inlineStr">
+      <c r="BF2" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG2" s="2" t="inlineStr"/>
-      <c r="BH2" s="2" t="inlineStr"/>
+      <c r="BG2" s="3" t="inlineStr"/>
+      <c r="BH2" s="3" t="inlineStr"/>
+      <c r="BI2" s="3" t="inlineStr"/>
+      <c r="BJ2" s="3" t="inlineStr"/>
+      <c r="BK2" s="3" t="inlineStr"/>
+      <c r="BL2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr"/>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>Cencora</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr"/>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>ServiceNow</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>2026-08-18T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>What: Public Safety Patrol When: August 19, 2026 1003H Where: Bluementritt cor. España Blvd. Status: Negative for flooded area as of 1003H Unit: DMAX3 T.O: B. Mendoza Crew: B. Santos (Source: Manila City DRRM Department) #ManilaPIO #AlertoManile</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr"/>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Wildfires and extreme heat show climate change is now Europe’s biggest security threat</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>天災</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>僅紀錄</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>待人工覆核</t>
         </is>
       </c>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O3" s="4" t="inlineStr">
-        <is>
-          <t>'-0.108</t>
-        </is>
-      </c>
-      <c r="P3" s="4" t="inlineStr"/>
-      <c r="Q3" s="4" t="inlineStr"/>
-      <c r="R3" s="4" t="inlineStr"/>
-      <c r="S3" s="4" t="inlineStr"/>
-      <c r="T3" s="4" t="inlineStr">
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>'-0.117</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr"/>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr">
         <is>
           <t>主體證據不足</t>
         </is>
       </c>
-      <c r="U3" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxNTXNvREY3UzJxS0ZXNnRQUy1XUGVneThKNTFMc2N6OXV4RGZRcEE3UXJjNzBHU3h1a1NqQnVMMTlRcEFDY3I3eFk3ZUlnVWJURGJUeFNoTjdGTEZ0QmItVlhENVpJMEs0Ymp0Sk5lUlNLNUc1SlNlNW0ybC1jZjR6Z0tiakJFYmMyNGVCenNGTW8tOFVrdGFVOG15NlhURTRNeTktaFM1TVNLWEtIdFVMZDY4UXJtR3p2S0ExZllRbVNTYkQ1djhrX0JpVUJMT1JINmxKUU00R3NCa2E5?oc=5</t>
-        </is>
-      </c>
-      <c r="V3" s="4" t="inlineStr">
-        <is>
-          <t>facebook.com</t>
-        </is>
-      </c>
-      <c r="W3" s="4" t="inlineStr"/>
-      <c r="X3" s="4" t="inlineStr">
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNVVV4eTNJanNDd1JqdUd6MUtINkQ1bXdaS1czelZ1OF9wdmRrZFdpR3hQU3l1aTV5RFpoUVg1bzVuTEY1Zm1Ic21Md2U2NzR3YS1GU21VRHNyemhCRTAxVTR4dmdyWTYtN1FrbzZDZXBfOElBdDd4aktsOS1aMGRXMFFZaFpEcS1sYVp5enJMMFRDTTJCY0w5bE41Wk5vdVREUGQ2Vm5vMl9pNU5KR05LUTRvSENsQnJGQXdB?oc=5</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>Chatham House</t>
+        </is>
+      </c>
+      <c r="W3" s="3" t="inlineStr"/>
+      <c r="X3" s="3" t="inlineStr">
         <is>
           <t>OPERATIONS</t>
         </is>
       </c>
-      <c r="Y3" s="4" t="inlineStr">
+      <c r="Y3" s="3" t="inlineStr">
         <is>
           <t>NATURAL_DISASTER</t>
         </is>
       </c>
-      <c r="Z3" s="4" t="inlineStr">
-        <is>
-          <t>flood</t>
-        </is>
-      </c>
-      <c r="AA3" s="4" t="inlineStr">
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>wildfire</t>
+        </is>
+      </c>
+      <c r="AA3" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB3" s="4" t="inlineStr"/>
-      <c r="AC3" s="4" t="inlineStr">
-        <is>
-          <t>304cbada68fbab61665c24fd</t>
-        </is>
-      </c>
-      <c r="AD3" s="4" t="inlineStr">
-        <is>
-          <t>cef13a3c747e25f7c286fb7c</t>
-        </is>
-      </c>
-      <c r="AE3" s="4" t="inlineStr"/>
-      <c r="AF3" s="4" t="inlineStr"/>
-      <c r="AG3" s="4" t="inlineStr"/>
-      <c r="AH3" s="4" t="inlineStr"/>
-      <c r="AI3" s="4" t="inlineStr"/>
-      <c r="AJ3" s="4" t="inlineStr"/>
-      <c r="AK3" s="4" t="inlineStr"/>
-      <c r="AL3" s="4" t="inlineStr"/>
-      <c r="AM3" s="4" t="inlineStr"/>
-      <c r="AN3" s="4" t="inlineStr"/>
-      <c r="AO3" s="4" t="inlineStr">
+      <c r="AB3" s="3" t="inlineStr"/>
+      <c r="AC3" s="3" t="inlineStr">
+        <is>
+          <t>46b57714c7435eb30433a2e4</t>
+        </is>
+      </c>
+      <c r="AD3" s="3" t="inlineStr">
+        <is>
+          <t>584d67c4f9af2372ea1714ff</t>
+        </is>
+      </c>
+      <c r="AE3" s="3" t="inlineStr"/>
+      <c r="AF3" s="3" t="inlineStr"/>
+      <c r="AG3" s="3" t="inlineStr"/>
+      <c r="AH3" s="3" t="inlineStr"/>
+      <c r="AI3" s="3" t="inlineStr"/>
+      <c r="AJ3" s="3" t="inlineStr"/>
+      <c r="AK3" s="3" t="inlineStr"/>
+      <c r="AL3" s="3" t="inlineStr"/>
+      <c r="AM3" s="3" t="inlineStr"/>
+      <c r="AN3" s="3" t="inlineStr"/>
+      <c r="AO3" s="3" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AP3" s="4" t="inlineStr"/>
-      <c r="AQ3" s="4" t="inlineStr"/>
-      <c r="AR3" s="4" t="inlineStr"/>
-      <c r="AS3" s="4" t="inlineStr"/>
-      <c r="AT3" s="4" t="inlineStr"/>
-      <c r="AU3" s="4" t="inlineStr"/>
-      <c r="AV3" s="4" t="inlineStr"/>
-      <c r="AW3" s="4" t="inlineStr"/>
-      <c r="AX3" s="4" t="inlineStr"/>
-      <c r="AY3" s="4" t="inlineStr"/>
-      <c r="AZ3" s="4" t="inlineStr"/>
-      <c r="BA3" s="4" t="inlineStr"/>
-      <c r="BB3" s="4" t="inlineStr">
-        <is>
-          <t>COR</t>
-        </is>
-      </c>
-      <c r="BC3" s="4" t="inlineStr">
+      <c r="AP3" s="3" t="inlineStr"/>
+      <c r="AQ3" s="3" t="inlineStr"/>
+      <c r="AR3" s="3" t="inlineStr"/>
+      <c r="AS3" s="3" t="inlineStr"/>
+      <c r="AT3" s="3" t="inlineStr"/>
+      <c r="AU3" s="3" t="inlineStr"/>
+      <c r="AV3" s="3" t="inlineStr"/>
+      <c r="AW3" s="3" t="inlineStr"/>
+      <c r="AX3" s="3" t="inlineStr"/>
+      <c r="AY3" s="3" t="inlineStr"/>
+      <c r="AZ3" s="3" t="inlineStr"/>
+      <c r="BA3" s="3" t="inlineStr"/>
+      <c r="BB3" s="3" t="inlineStr">
+        <is>
+          <t>NOW</t>
+        </is>
+      </c>
+      <c r="BC3" s="3" t="inlineStr">
         <is>
           <t>主體證據不足</t>
         </is>
       </c>
-      <c r="BD3" s="4" t="inlineStr">
-        <is>
-          <t>COR</t>
-        </is>
-      </c>
-      <c r="BE3" s="4" t="inlineStr">
+      <c r="BD3" s="3" t="inlineStr">
+        <is>
+          <t>NOW</t>
+        </is>
+      </c>
+      <c r="BE3" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF3" s="4" t="inlineStr">
+      <c r="BF3" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG3" s="4" t="inlineStr"/>
-      <c r="BH3" s="4" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr"/>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>ServiceNow</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-18T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>Wildfires and extreme heat show climate change is now Europe’s biggest security threat</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>天災</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>僅紀錄</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M4" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O4" s="4" t="inlineStr">
-        <is>
-          <t>'-0.117</t>
-        </is>
-      </c>
-      <c r="P4" s="4" t="inlineStr"/>
-      <c r="Q4" s="4" t="inlineStr"/>
-      <c r="R4" s="4" t="inlineStr"/>
-      <c r="S4" s="4" t="inlineStr"/>
-      <c r="T4" s="4" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U4" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNVVV4eTNJanNDd1JqdUd6MUtINkQ1bXdaS1czelZ1OF9wdmRrZFdpR3hQU3l1aTV5RFpoUVg1bzVuTEY1Zm1Ic21Md2U2NzR3YS1GU21VRHNyemhCRTAxVTR4dmdyWTYtN1FrbzZDZXBfOElBdDd4aktsOS1aMGRXMFFZaFpEcS1sYVp5enJMMFRDTTJCY0w5bE41Wk5vdVREUGQ2Vm5vMl9pNU5KR05LUTRvSENsQnJGQXdB?oc=5</t>
-        </is>
-      </c>
-      <c r="V4" s="4" t="inlineStr">
-        <is>
-          <t>Chatham House</t>
-        </is>
-      </c>
-      <c r="W4" s="4" t="inlineStr"/>
-      <c r="X4" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y4" s="4" t="inlineStr">
-        <is>
-          <t>NATURAL_DISASTER</t>
-        </is>
-      </c>
-      <c r="Z4" s="4" t="inlineStr">
-        <is>
-          <t>wildfire</t>
-        </is>
-      </c>
-      <c r="AA4" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="4" t="inlineStr"/>
-      <c r="AC4" s="4" t="inlineStr">
-        <is>
-          <t>46b57714c7435eb30433a2e4</t>
-        </is>
-      </c>
-      <c r="AD4" s="4" t="inlineStr">
-        <is>
-          <t>584d67c4f9af2372ea1714ff</t>
-        </is>
-      </c>
-      <c r="AE4" s="4" t="inlineStr"/>
-      <c r="AF4" s="4" t="inlineStr"/>
-      <c r="AG4" s="4" t="inlineStr"/>
-      <c r="AH4" s="4" t="inlineStr"/>
-      <c r="AI4" s="4" t="inlineStr"/>
-      <c r="AJ4" s="4" t="inlineStr"/>
-      <c r="AK4" s="4" t="inlineStr"/>
-      <c r="AL4" s="4" t="inlineStr"/>
-      <c r="AM4" s="4" t="inlineStr"/>
-      <c r="AN4" s="4" t="inlineStr"/>
-      <c r="AO4" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP4" s="4" t="inlineStr"/>
-      <c r="AQ4" s="4" t="inlineStr"/>
-      <c r="AR4" s="4" t="inlineStr"/>
-      <c r="AS4" s="4" t="inlineStr"/>
-      <c r="AT4" s="4" t="inlineStr"/>
-      <c r="AU4" s="4" t="inlineStr"/>
-      <c r="AV4" s="4" t="inlineStr"/>
-      <c r="AW4" s="4" t="inlineStr"/>
-      <c r="AX4" s="4" t="inlineStr"/>
-      <c r="AY4" s="4" t="inlineStr"/>
-      <c r="AZ4" s="4" t="inlineStr"/>
-      <c r="BA4" s="4" t="inlineStr"/>
-      <c r="BB4" s="4" t="inlineStr">
-        <is>
-          <t>NOW</t>
-        </is>
-      </c>
-      <c r="BC4" s="4" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD4" s="4" t="inlineStr">
-        <is>
-          <t>NOW</t>
-        </is>
-      </c>
-      <c r="BE4" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF4" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG4" s="4" t="inlineStr"/>
-      <c r="BH4" s="4" t="inlineStr"/>
+      <c r="BG3" s="3" t="inlineStr"/>
+      <c r="BH3" s="3" t="inlineStr"/>
+      <c r="BI3" s="3" t="inlineStr"/>
+      <c r="BJ3" s="3" t="inlineStr"/>
+      <c r="BK3" s="3" t="inlineStr"/>
+      <c r="BL3" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH4"/>
+  <autoFilter ref="A1:BL3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4498,7 +4276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH1"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4561,6 +4339,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4864,9 +4646,29 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH1"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4877,7 +4679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA5"/>
+  <dimension ref="A1:AA8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4927,477 +4729,768 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>methods</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>started_at</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>finished_at</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>llm_calls</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>cache_reused</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>selected_company_count</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>collected</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>rows</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>errors</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>stages</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>quota_reserved</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>重複合併</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>sources</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>rows</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>changed</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>missing_publication_time</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>ticker_statuses</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>llm_calls</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>start</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>end</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>methods</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>ai</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>cache_reused</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>major</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>selected_company_count</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>collected</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>errors</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>stages</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>quota_reserved</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>重複合併</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>ticker-audit-20261024-081549</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>ticker-audit</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>daily-2026-10-26</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>schedule</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T08:15:49.296780+08:00</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T08:15:49.296790+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="G2" s="4" t="n">
-        <v>1691</v>
-      </c>
-      <c r="H2" s="4" t="n">
-        <v>257</v>
-      </c>
-      <c r="I2" s="4" t="n">
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:23:38.366332+08:00</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:40:53.776257+08:00</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="L2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="4" t="inlineStr">
-        <is>
-          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
-        </is>
-      </c>
-      <c r="K2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="4" t="inlineStr"/>
-      <c r="M2" s="4" t="inlineStr"/>
-      <c r="N2" s="4" t="inlineStr"/>
-      <c r="O2" s="4" t="inlineStr"/>
-      <c r="P2" s="4" t="inlineStr"/>
-      <c r="Q2" s="4" t="inlineStr"/>
-      <c r="R2" s="4" t="inlineStr"/>
-      <c r="S2" s="4" t="inlineStr"/>
-      <c r="T2" s="4" t="inlineStr"/>
-      <c r="U2" s="4" t="inlineStr"/>
-      <c r="V2" s="4" t="inlineStr"/>
-      <c r="W2" s="4" t="inlineStr"/>
-      <c r="X2" s="4" t="inlineStr"/>
-      <c r="Y2" s="4" t="inlineStr"/>
-      <c r="Z2" s="4" t="inlineStr"/>
-      <c r="AA2" s="4" t="inlineStr"/>
+      <c r="M2" s="3" t="n">
+        <v>1926</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="P2" s="3" t="n">
+        <v>503</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>1976</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>1961</v>
+      </c>
+      <c r="S2" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>['方法一 16 筆', '方法二 1958 筆；公司 503 家（非輪替）', '市場事件搜尋 2 筆', 'FinBERT 完成 1976 筆']</t>
+        </is>
+      </c>
+      <c r="U2" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="V2" s="3" t="n">
+        <v>1961</v>
+      </c>
+      <c r="W2" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="X2" s="3" t="inlineStr"/>
+      <c r="Y2" s="3" t="inlineStr"/>
+      <c r="Z2" s="3" t="inlineStr"/>
+      <c r="AA2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>daily-2026-10-25</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>schedule</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:26:34.299718+08:00</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:32:11.776786+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr"/>
-      <c r="G3" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="H3" s="4" t="inlineStr"/>
-      <c r="I3" s="4" t="inlineStr"/>
-      <c r="J3" s="4" t="inlineStr"/>
-      <c r="K3" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-22T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="O3" s="4" t="inlineStr"/>
-      <c r="P3" s="4" t="b">
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="Q3" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="R3" s="4" t="n">
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:23:17.137147+08:00</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:40:12.120180+08:00</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="L3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="S3" s="4" t="n">
-        <v>48</v>
-      </c>
-      <c r="T3" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="U3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" s="4" t="inlineStr">
+      <c r="M3" s="3" t="n">
+        <v>2032</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>503</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>2089</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>2067</v>
+      </c>
+      <c r="S3" s="3" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="X3" s="4" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
-      </c>
-      <c r="Y3" s="4" t="n">
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>['方法一 26 筆', '方法二 2059 筆；公司 503 家（非輪替）', '市場事件搜尋 6 筆', 'FinBERT 完成 2089 筆']</t>
+        </is>
+      </c>
+      <c r="U3" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="Z3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="V3" s="3" t="n">
+        <v>2067</v>
+      </c>
+      <c r="W3" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="X3" s="3" t="inlineStr"/>
+      <c r="Y3" s="3" t="inlineStr"/>
+      <c r="Z3" s="3" t="inlineStr"/>
+      <c r="AA3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>daily-2026-10-24</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>schedule</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:20:47.845317+08:00</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:21:20.302846+08:00</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="4" t="inlineStr"/>
-      <c r="J4" s="4" t="inlineStr"/>
-      <c r="K4" s="4" t="n">
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M4" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O4" s="4" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P4" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="R4" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="S4" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="T4" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="U4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="V4" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="W4" s="4" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T12:44:09.884829+08:00</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T13:04:34.984103+08:00</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>3760</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>503</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>3802</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>3825</v>
+      </c>
+      <c r="S4" s="3" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="X4" s="4" t="inlineStr">
-        <is>
-          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
-        </is>
-      </c>
-      <c r="Y4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA4" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>['方法一 158 筆', '方法二 3638 筆；公司 503 家（非輪替）', '市場事件搜尋 8 筆', 'FinBERT 完成 3802 筆']</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="V4" s="3" t="n">
+        <v>3793</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="X4" s="3" t="inlineStr"/>
+      <c r="Y4" s="3" t="inlineStr"/>
+      <c r="Z4" s="3" t="inlineStr"/>
+      <c r="AA4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>ticker-audit-20261024-081549</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>ticker-audit</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296780+08:00</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296790+08:00</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="3" t="inlineStr"/>
+      <c r="M5" s="3" t="inlineStr"/>
+      <c r="N5" s="3" t="inlineStr"/>
+      <c r="O5" s="3" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="n">
+        <v>1691</v>
+      </c>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr"/>
+      <c r="V5" s="3" t="inlineStr"/>
+      <c r="W5" s="3" t="inlineStr"/>
+      <c r="X5" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y5" s="3" t="n">
+        <v>257</v>
+      </c>
+      <c r="Z5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:34.299718+08:00</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:32:11.776786+08:00</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="S6" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T6" s="3" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U6" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="V6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="3" t="inlineStr"/>
+      <c r="Y6" s="3" t="inlineStr"/>
+      <c r="Z6" s="3" t="inlineStr"/>
+      <c r="AA6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:20:47.845317+08:00</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:21:20.302846+08:00</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="S7" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T7" s="3" t="inlineStr">
+        <is>
+          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
+        </is>
+      </c>
+      <c r="U7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="W7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="3" t="inlineStr"/>
+      <c r="Y7" s="3" t="inlineStr"/>
+      <c r="Z7" s="3" t="inlineStr"/>
+      <c r="AA7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:19:11.949238+08:00</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:19:18.833437+08:00</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr"/>
-      <c r="G5" s="4" t="n">
+      <c r="K8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="H5" s="4" t="inlineStr"/>
-      <c r="I5" s="4" t="inlineStr"/>
-      <c r="J5" s="4" t="inlineStr"/>
-      <c r="K5" s="4" t="n">
+      <c r="M8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M5" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O5" s="4" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P5" s="4" t="b">
+      <c r="N8" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="S8" s="3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T8" s="3" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U8" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="Q5" s="4" t="n">
-        <v>33</v>
-      </c>
-      <c r="R5" s="4" t="n">
+      <c r="V8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="S5" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="T5" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="U5" s="4" t="n">
+      <c r="W8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="V5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" s="4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X5" s="4" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
-      </c>
-      <c r="Y5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="X8" s="3" t="inlineStr"/>
+      <c r="Y8" s="3" t="inlineStr"/>
+      <c r="Z8" s="3" t="inlineStr"/>
+      <c r="AA8" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA5"/>
+  <autoFilter ref="A1:AA8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/news_daily/2026-08-18.xlsx
+++ b/news_daily/2026-08-18.xlsx
@@ -16,7 +16,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
   </definedNames>
@@ -1442,32 +1442,32 @@
       <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
@@ -1520,7 +1520,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB5" s="3" t="inlineStr"/>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>26c16020289b416b864621c3fea9530c</t>
+        </is>
+      </c>
       <c r="AC5" s="3" t="inlineStr">
         <is>
           <t>304cbada68fbab61665c24fd</t>
@@ -1543,7 +1547,7 @@
       <c r="AN5" s="3" t="inlineStr"/>
       <c r="AO5" s="3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP5" s="3" t="inlineStr"/>
@@ -1585,10 +1589,22 @@
       </c>
       <c r="BG5" s="3" t="inlineStr"/>
       <c r="BH5" s="3" t="inlineStr"/>
-      <c r="BI5" s="3" t="inlineStr"/>
+      <c r="BI5" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ5" s="3" t="inlineStr"/>
-      <c r="BK5" s="3" t="inlineStr"/>
-      <c r="BL5" s="3" t="inlineStr"/>
+      <c r="BK5" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -1620,32 +1636,32 @@
       <c r="G6" s="3" t="inlineStr"/>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
@@ -1685,7 +1701,7 @@
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
@@ -1698,7 +1714,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB6" s="3" t="inlineStr"/>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>f547c4734a7f4598afecf735dd5f246d</t>
+        </is>
+      </c>
       <c r="AC6" s="3" t="inlineStr">
         <is>
           <t>46b57714c7435eb30433a2e4</t>
@@ -1721,7 +1741,7 @@
       <c r="AN6" s="3" t="inlineStr"/>
       <c r="AO6" s="3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP6" s="3" t="inlineStr"/>
@@ -1763,10 +1783,22 @@
       </c>
       <c r="BG6" s="3" t="inlineStr"/>
       <c r="BH6" s="3" t="inlineStr"/>
-      <c r="BI6" s="3" t="inlineStr"/>
+      <c r="BI6" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ6" s="3" t="inlineStr"/>
-      <c r="BK6" s="3" t="inlineStr"/>
-      <c r="BL6" s="3" t="inlineStr"/>
+      <c r="BK6" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -3517,7 +3549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL3"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3908,364 +3940,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr"/>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>Cencora</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-18T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>What: Public Safety Patrol When: August 19, 2026 1003H Where: Bluementritt cor. España Blvd. Status: Negative for flooded area as of 1003H Unit: DMAX3 T.O: B. Mendoza Crew: B. Santos (Source: Manila City DRRM Department) #ManilaPIO #AlertoManile</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr"/>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>天災</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>僅紀錄</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>'-0.108</t>
-        </is>
-      </c>
-      <c r="P2" s="3" t="inlineStr"/>
-      <c r="Q2" s="3" t="inlineStr"/>
-      <c r="R2" s="3" t="inlineStr"/>
-      <c r="S2" s="3" t="inlineStr"/>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxNTXNvREY3UzJxS0ZXNnRQUy1XUGVneThKNTFMc2N6OXV4RGZRcEE3UXJjNzBHU3h1a1NqQnVMMTlRcEFDY3I3eFk3ZUlnVWJURGJUeFNoTjdGTEZ0QmItVlhENVpJMEs0Ymp0Sk5lUlNLNUc1SlNlNW0ybC1jZjR6Z0tiakJFYmMyNGVCenNGTW8tOFVrdGFVOG15NlhURTRNeTktaFM1TVNLWEtIdFVMZDY4UXJtR3p2S0ExZllRbVNTYkQ1djhrX0JpVUJMT1JINmxKUU00R3NCa2E5?oc=5</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>facebook.com</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr"/>
-      <c r="X2" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y2" s="3" t="inlineStr">
-        <is>
-          <t>NATURAL_DISASTER</t>
-        </is>
-      </c>
-      <c r="Z2" s="3" t="inlineStr">
-        <is>
-          <t>flood</t>
-        </is>
-      </c>
-      <c r="AA2" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="3" t="inlineStr"/>
-      <c r="AC2" s="3" t="inlineStr">
-        <is>
-          <t>304cbada68fbab61665c24fd</t>
-        </is>
-      </c>
-      <c r="AD2" s="3" t="inlineStr">
-        <is>
-          <t>cef13a3c747e25f7c286fb7c</t>
-        </is>
-      </c>
-      <c r="AE2" s="3" t="inlineStr"/>
-      <c r="AF2" s="3" t="inlineStr"/>
-      <c r="AG2" s="3" t="inlineStr"/>
-      <c r="AH2" s="3" t="inlineStr"/>
-      <c r="AI2" s="3" t="inlineStr"/>
-      <c r="AJ2" s="3" t="inlineStr"/>
-      <c r="AK2" s="3" t="inlineStr"/>
-      <c r="AL2" s="3" t="inlineStr"/>
-      <c r="AM2" s="3" t="inlineStr"/>
-      <c r="AN2" s="3" t="inlineStr"/>
-      <c r="AO2" s="3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP2" s="3" t="inlineStr"/>
-      <c r="AQ2" s="3" t="inlineStr"/>
-      <c r="AR2" s="3" t="inlineStr"/>
-      <c r="AS2" s="3" t="inlineStr"/>
-      <c r="AT2" s="3" t="inlineStr"/>
-      <c r="AU2" s="3" t="inlineStr"/>
-      <c r="AV2" s="3" t="inlineStr"/>
-      <c r="AW2" s="3" t="inlineStr"/>
-      <c r="AX2" s="3" t="inlineStr"/>
-      <c r="AY2" s="3" t="inlineStr"/>
-      <c r="AZ2" s="3" t="inlineStr"/>
-      <c r="BA2" s="3" t="inlineStr"/>
-      <c r="BB2" s="3" t="inlineStr">
-        <is>
-          <t>COR</t>
-        </is>
-      </c>
-      <c r="BC2" s="3" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD2" s="3" t="inlineStr">
-        <is>
-          <t>COR</t>
-        </is>
-      </c>
-      <c r="BE2" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF2" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG2" s="3" t="inlineStr"/>
-      <c r="BH2" s="3" t="inlineStr"/>
-      <c r="BI2" s="3" t="inlineStr"/>
-      <c r="BJ2" s="3" t="inlineStr"/>
-      <c r="BK2" s="3" t="inlineStr"/>
-      <c r="BL2" s="3" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>ServiceNow</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-18T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Wildfires and extreme heat show climate change is now Europe’s biggest security threat</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>天災</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>僅紀錄</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>'-0.117</t>
-        </is>
-      </c>
-      <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="3" t="inlineStr"/>
-      <c r="S3" s="3" t="inlineStr"/>
-      <c r="T3" s="3" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U3" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNVVV4eTNJanNDd1JqdUd6MUtINkQ1bXdaS1czelZ1OF9wdmRrZFdpR3hQU3l1aTV5RFpoUVg1bzVuTEY1Zm1Ic21Md2U2NzR3YS1GU21VRHNyemhCRTAxVTR4dmdyWTYtN1FrbzZDZXBfOElBdDd4aktsOS1aMGRXMFFZaFpEcS1sYVp5enJMMFRDTTJCY0w5bE41Wk5vdVREUGQ2Vm5vMl9pNU5KR05LUTRvSENsQnJGQXdB?oc=5</t>
-        </is>
-      </c>
-      <c r="V3" s="3" t="inlineStr">
-        <is>
-          <t>Chatham House</t>
-        </is>
-      </c>
-      <c r="W3" s="3" t="inlineStr"/>
-      <c r="X3" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y3" s="3" t="inlineStr">
-        <is>
-          <t>NATURAL_DISASTER</t>
-        </is>
-      </c>
-      <c r="Z3" s="3" t="inlineStr">
-        <is>
-          <t>wildfire</t>
-        </is>
-      </c>
-      <c r="AA3" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="3" t="inlineStr"/>
-      <c r="AC3" s="3" t="inlineStr">
-        <is>
-          <t>46b57714c7435eb30433a2e4</t>
-        </is>
-      </c>
-      <c r="AD3" s="3" t="inlineStr">
-        <is>
-          <t>584d67c4f9af2372ea1714ff</t>
-        </is>
-      </c>
-      <c r="AE3" s="3" t="inlineStr"/>
-      <c r="AF3" s="3" t="inlineStr"/>
-      <c r="AG3" s="3" t="inlineStr"/>
-      <c r="AH3" s="3" t="inlineStr"/>
-      <c r="AI3" s="3" t="inlineStr"/>
-      <c r="AJ3" s="3" t="inlineStr"/>
-      <c r="AK3" s="3" t="inlineStr"/>
-      <c r="AL3" s="3" t="inlineStr"/>
-      <c r="AM3" s="3" t="inlineStr"/>
-      <c r="AN3" s="3" t="inlineStr"/>
-      <c r="AO3" s="3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP3" s="3" t="inlineStr"/>
-      <c r="AQ3" s="3" t="inlineStr"/>
-      <c r="AR3" s="3" t="inlineStr"/>
-      <c r="AS3" s="3" t="inlineStr"/>
-      <c r="AT3" s="3" t="inlineStr"/>
-      <c r="AU3" s="3" t="inlineStr"/>
-      <c r="AV3" s="3" t="inlineStr"/>
-      <c r="AW3" s="3" t="inlineStr"/>
-      <c r="AX3" s="3" t="inlineStr"/>
-      <c r="AY3" s="3" t="inlineStr"/>
-      <c r="AZ3" s="3" t="inlineStr"/>
-      <c r="BA3" s="3" t="inlineStr"/>
-      <c r="BB3" s="3" t="inlineStr">
-        <is>
-          <t>NOW</t>
-        </is>
-      </c>
-      <c r="BC3" s="3" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD3" s="3" t="inlineStr">
-        <is>
-          <t>NOW</t>
-        </is>
-      </c>
-      <c r="BE3" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF3" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG3" s="3" t="inlineStr"/>
-      <c r="BH3" s="3" t="inlineStr"/>
-      <c r="BI3" s="3" t="inlineStr"/>
-      <c r="BJ3" s="3" t="inlineStr"/>
-      <c r="BK3" s="3" t="inlineStr"/>
-      <c r="BL3" s="3" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:BL3"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/news_daily/2026-08-18.xlsx
+++ b/news_daily/2026-08-18.xlsx
@@ -1268,28 +1268,32 @@
       <c r="G4" s="3" t="inlineStr"/>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -1329,7 +1333,7 @@
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z4" s="3" t="inlineStr">
@@ -1342,7 +1346,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB4" s="3" t="inlineStr"/>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>7f4e6bd0009b49faa714f28fe1db1997</t>
+        </is>
+      </c>
       <c r="AC4" s="3" t="inlineStr">
         <is>
           <t>cdaff806a3e2c472542a3b8e</t>
@@ -1363,7 +1371,11 @@
       <c r="AL4" s="3" t="inlineStr"/>
       <c r="AM4" s="3" t="inlineStr"/>
       <c r="AN4" s="3" t="inlineStr"/>
-      <c r="AO4" s="3" t="inlineStr"/>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP4" s="3" t="inlineStr"/>
       <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr"/>
@@ -1407,10 +1419,22 @@
         </is>
       </c>
       <c r="BH4" s="3" t="inlineStr"/>
-      <c r="BI4" s="3" t="inlineStr"/>
+      <c r="BI4" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ4" s="3" t="inlineStr"/>
-      <c r="BK4" s="3" t="inlineStr"/>
-      <c r="BL4" s="3" t="inlineStr"/>
+      <c r="BK4" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -1834,28 +1858,32 @@
       <c r="G7" s="3" t="inlineStr"/>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>股價下跌</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
@@ -1895,7 +1923,7 @@
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t>PRICE_MOVEMENT</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
@@ -1908,7 +1936,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB7" s="3" t="inlineStr"/>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>982915dce0cd432f833e2b828bb733e1</t>
+        </is>
+      </c>
       <c r="AC7" s="3" t="inlineStr">
         <is>
           <t>aea408fe3f0396b31a2d526d</t>
@@ -1929,7 +1961,11 @@
       <c r="AL7" s="3" t="inlineStr"/>
       <c r="AM7" s="3" t="inlineStr"/>
       <c r="AN7" s="3" t="inlineStr"/>
-      <c r="AO7" s="3" t="inlineStr"/>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP7" s="3" t="inlineStr"/>
       <c r="AQ7" s="3" t="inlineStr"/>
       <c r="AR7" s="3" t="inlineStr"/>
@@ -1973,10 +2009,22 @@
         </is>
       </c>
       <c r="BH7" s="3" t="inlineStr"/>
-      <c r="BI7" s="3" t="inlineStr"/>
+      <c r="BI7" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ7" s="3" t="inlineStr"/>
-      <c r="BK7" s="3" t="inlineStr"/>
-      <c r="BL7" s="3" t="inlineStr"/>
+      <c r="BK7" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
